--- a/Team-Data/2010-11/3-31-2010-11.xlsx
+++ b/Team-Data/2010-11/3-31-2010-11.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" t="n">
         <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.573</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J2" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L2" t="n">
         <v>6.3</v>
@@ -691,28 +758,28 @@
         <v>17.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O2" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T2" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U2" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V2" t="n">
         <v>13.6</v>
@@ -730,13 +797,13 @@
         <v>18.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>3</v>
@@ -769,7 +836,7 @@
         <v>16</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -790,16 +857,16 @@
         <v>26</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
         <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY2" t="n">
         <v>5</v>
@@ -808,10 +875,10 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -843,46 +910,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
         <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>0.708</v>
+        <v>0.699</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>76.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M3" t="n">
         <v>13.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O3" t="n">
         <v>17.9</v>
       </c>
       <c r="P3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>7.9</v>
@@ -894,16 +961,16 @@
         <v>38.9</v>
       </c>
       <c r="U3" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V3" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
@@ -915,28 +982,28 @@
         <v>20.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AD3" t="n">
         <v>29</v>
       </c>
       <c r="AE3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF3" t="n">
         <v>5</v>
       </c>
-      <c r="AF3" t="n">
-        <v>4</v>
-      </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH3" t="n">
         <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -951,10 +1018,10 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
@@ -975,16 +1042,16 @@
         <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>16</v>
@@ -993,10 +1060,10 @@
         <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
         <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>0.438</v>
+        <v>0.432</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J4" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L4" t="n">
         <v>4.8</v>
@@ -1055,7 +1122,7 @@
         <v>14.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="O4" t="n">
         <v>18.8</v>
@@ -1064,22 +1131,22 @@
         <v>24.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.753</v>
+        <v>0.756</v>
       </c>
       <c r="R4" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
         <v>30.2</v>
       </c>
       <c r="T4" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U4" t="n">
         <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>6.3</v>
@@ -1088,7 +1155,7 @@
         <v>5.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z4" t="n">
         <v>20.2</v>
@@ -1097,13 +1164,13 @@
         <v>21.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.7</v>
+        <v>-3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
@@ -1136,25 +1203,25 @@
         <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT4" t="n">
         <v>19</v>
       </c>
       <c r="AU4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>24</v>
@@ -1163,16 +1230,16 @@
         <v>28</v>
       </c>
       <c r="AX4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" t="n">
         <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,7 +1292,7 @@
         <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>80.5</v>
+        <v>80.7</v>
       </c>
       <c r="K5" t="n">
         <v>0.46</v>
@@ -1237,7 +1304,7 @@
         <v>17.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O5" t="n">
         <v>18.1</v>
@@ -1246,7 +1313,7 @@
         <v>24.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="R5" t="n">
         <v>12</v>
@@ -1255,7 +1322,7 @@
         <v>32.4</v>
       </c>
       <c r="T5" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U5" t="n">
         <v>22</v>
@@ -1264,7 +1331,7 @@
         <v>14.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X5" t="n">
         <v>5.8</v>
@@ -1273,19 +1340,19 @@
         <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1300,22 +1367,22 @@
         <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
         <v>16</v>
       </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
         <v>15</v>
@@ -1336,7 +1403,7 @@
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
         <v>16</v>
@@ -1345,13 +1412,13 @@
         <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>22</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
         <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>0.192</v>
+        <v>0.203</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
@@ -1419,7 +1486,7 @@
         <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O6" t="n">
         <v>18.7</v>
@@ -1428,7 +1495,7 @@
         <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R6" t="n">
         <v>10.5</v>
@@ -1443,16 +1510,16 @@
         <v>20.9</v>
       </c>
       <c r="V6" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W6" t="n">
         <v>6.7</v>
       </c>
       <c r="X6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z6" t="n">
         <v>20</v>
@@ -1464,10 +1531,10 @@
         <v>94.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>-10.1</v>
+        <v>-9.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
         <v>30</v>
@@ -1491,13 +1558,13 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM6" t="n">
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
         <v>12</v>
@@ -1515,22 +1582,22 @@
         <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ6" t="n">
         <v>8</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -1574,43 +1641,43 @@
         <v>74</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.703</v>
+        <v>0.716</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J7" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.473</v>
+        <v>0.476</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O7" t="n">
         <v>17.6</v>
       </c>
       <c r="P7" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="R7" t="n">
         <v>9.4</v>
@@ -1622,13 +1689,13 @@
         <v>41.2</v>
       </c>
       <c r="U7" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V7" t="n">
         <v>13.8</v>
       </c>
       <c r="W7" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X7" t="n">
         <v>4.3</v>
@@ -1637,40 +1704,40 @@
         <v>3.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
         <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.90000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE7" t="n">
         <v>3</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>4</v>
       </c>
-      <c r="AF7" t="n">
-        <v>5</v>
-      </c>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
         <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1679,10 +1746,10 @@
         <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
         <v>26</v>
@@ -1700,16 +1767,16 @@
         <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX7" t="n">
         <v>24</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>25</v>
       </c>
       <c r="AY7" t="n">
         <v>2</v>
@@ -1721,7 +1788,7 @@
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1774,40 +1841,40 @@
         <v>80.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M8" t="n">
         <v>20.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.39</v>
+        <v>0.389</v>
       </c>
       <c r="O8" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="P8" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.772</v>
+        <v>0.773</v>
       </c>
       <c r="R8" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S8" t="n">
         <v>32.3</v>
       </c>
       <c r="T8" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U8" t="n">
         <v>22</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W8" t="n">
         <v>7.3</v>
@@ -1819,19 +1886,19 @@
         <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB8" t="n">
         <v>107.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1846,13 +1913,13 @@
         <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
@@ -1873,7 +1940,7 @@
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
         <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>0.356</v>
+        <v>0.351</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1959,25 +2026,25 @@
         <v>0.456</v>
       </c>
       <c r="L9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M9" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O9" t="n">
         <v>16.3</v>
       </c>
       <c r="P9" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.734</v>
+        <v>0.73</v>
       </c>
       <c r="R9" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S9" t="n">
         <v>27.1</v>
@@ -1989,7 +2056,7 @@
         <v>20.9</v>
       </c>
       <c r="V9" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W9" t="n">
         <v>7.2</v>
@@ -2004,7 +2071,7 @@
         <v>19.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB9" t="n">
         <v>96.2</v>
@@ -2013,7 +2080,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2028,7 +2095,7 @@
         <v>6</v>
       </c>
       <c r="AI9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
         <v>13</v>
@@ -2040,7 +2107,7 @@
         <v>20</v>
       </c>
       <c r="AM9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN9" t="n">
         <v>4</v>
@@ -2052,7 +2119,7 @@
         <v>28</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
@@ -2064,7 +2131,7 @@
         <v>30</v>
       </c>
       <c r="AU9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.413</v>
+        <v>0.421</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="J10" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L10" t="n">
         <v>8.4</v>
@@ -2150,19 +2217,19 @@
         <v>0.393</v>
       </c>
       <c r="O10" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P10" t="n">
         <v>20.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R10" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S10" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T10" t="n">
         <v>40.3</v>
@@ -2171,7 +2238,7 @@
         <v>22.4</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W10" t="n">
         <v>9</v>
@@ -2183,25 +2250,25 @@
         <v>4.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA10" t="n">
         <v>18.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>102.9</v>
+        <v>103.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.1</v>
+        <v>-3</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF10" t="n">
         <v>21</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>21</v>
@@ -2234,7 +2301,7 @@
         <v>30</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
         <v>11</v>
@@ -2243,10 +2310,10 @@
         <v>26</v>
       </c>
       <c r="AT10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
         <v>25</v>
@@ -2255,16 +2322,16 @@
         <v>2</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
         <v>7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E11" t="n">
         <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>0.534</v>
+        <v>0.52</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,7 +2384,7 @@
         <v>38.6</v>
       </c>
       <c r="J11" t="n">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="K11" t="n">
         <v>0.454</v>
@@ -2326,34 +2393,34 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O11" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="P11" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.798</v>
+        <v>0.8</v>
       </c>
       <c r="R11" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S11" t="n">
         <v>30.9</v>
       </c>
       <c r="T11" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U11" t="n">
         <v>23.6</v>
       </c>
       <c r="V11" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W11" t="n">
         <v>7.2</v>
@@ -2368,16 +2435,16 @@
         <v>20.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>105.6</v>
+        <v>106</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2389,10 +2456,10 @@
         <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ11" t="n">
         <v>3</v>
@@ -2407,16 +2474,16 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
         <v>8</v>
@@ -2428,25 +2495,25 @@
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV11" t="n">
         <v>6</v>
       </c>
       <c r="AW11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
         <v>18</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ11" t="n">
         <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" t="n">
         <v>34</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>0.453</v>
+        <v>0.447</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J12" t="n">
         <v>82.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L12" t="n">
         <v>7.1</v>
@@ -2520,22 +2587,22 @@
         <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
         <v>19.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W12" t="n">
         <v>7.1</v>
@@ -2547,16 +2614,16 @@
         <v>5.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA12" t="n">
         <v>21.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2577,10 +2644,10 @@
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>10</v>
@@ -2589,7 +2656,7 @@
         <v>9</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
         <v>7</v>
@@ -2607,7 +2674,7 @@
         <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
         <v>29</v>
@@ -2631,7 +2698,7 @@
         <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
         <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>0.392</v>
+        <v>0.387</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2681,7 +2748,7 @@
         <v>36.8</v>
       </c>
       <c r="J13" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K13" t="n">
         <v>0.458</v>
@@ -2693,7 +2760,7 @@
         <v>18.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O13" t="n">
         <v>19.1</v>
@@ -2702,19 +2769,19 @@
         <v>26.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.712</v>
+        <v>0.711</v>
       </c>
       <c r="R13" t="n">
         <v>11.6</v>
       </c>
       <c r="S13" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T13" t="n">
         <v>42.1</v>
       </c>
       <c r="U13" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V13" t="n">
         <v>16.3</v>
@@ -2735,10 +2802,10 @@
         <v>22.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="AD13" t="n">
         <v>3</v>
@@ -2759,7 +2826,7 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
         <v>18</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
         <v>15</v>
@@ -2795,16 +2862,16 @@
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW13" t="n">
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
@@ -2813,7 +2880,7 @@
         <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2930,7 @@
         <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.466</v>
@@ -2872,34 +2939,34 @@
         <v>6.4</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.781</v>
+        <v>0.784</v>
       </c>
       <c r="R14" t="n">
         <v>12.2</v>
       </c>
       <c r="S14" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U14" t="n">
         <v>22.1</v>
       </c>
       <c r="V14" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>7.4</v>
@@ -2914,22 +2981,22 @@
         <v>18.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>3</v>
@@ -2941,10 +3008,10 @@
         <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
@@ -2956,10 +3023,10 @@
         <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ14" t="n">
         <v>6</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
         <v>3</v>
@@ -2977,22 +3044,22 @@
         <v>12</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" t="n">
         <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
@@ -3045,7 +3112,7 @@
         <v>39.1</v>
       </c>
       <c r="J15" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K15" t="n">
         <v>0.47</v>
@@ -3054,10 +3121,10 @@
         <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="O15" t="n">
         <v>18.2</v>
@@ -3066,7 +3133,7 @@
         <v>24.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R15" t="n">
         <v>11.8</v>
@@ -3078,7 +3145,7 @@
         <v>40.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13.8</v>
@@ -3093,7 +3160,7 @@
         <v>6.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA15" t="n">
         <v>21.3</v>
@@ -3102,22 +3169,22 @@
         <v>100.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
         <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI15" t="n">
         <v>3</v>
@@ -3138,13 +3205,13 @@
         <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>7</v>
@@ -3156,7 +3223,7 @@
         <v>18</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>13</v>
@@ -3174,7 +3241,7 @@
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>0.699</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J16" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.48</v>
+        <v>0.479</v>
       </c>
       <c r="L16" t="n">
         <v>6.7</v>
@@ -3239,31 +3306,31 @@
         <v>18.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="O16" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P16" t="n">
         <v>28.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R16" t="n">
         <v>9.6</v>
       </c>
       <c r="S16" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T16" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W16" t="n">
         <v>6.6</v>
@@ -3278,31 +3345,31 @@
         <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>102.5</v>
+        <v>102.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG16" t="n">
         <v>6</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>13</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO16" t="n">
         <v>3</v>
@@ -3326,10 +3393,10 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS16" t="n">
         <v>2</v>
@@ -3341,19 +3408,19 @@
         <v>27</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
         <v>25</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
         <v>30</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>0.411</v>
+        <v>0.405</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3418,7 +3485,7 @@
         <v>5.9</v>
       </c>
       <c r="M17" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N17" t="n">
         <v>0.346</v>
@@ -3427,10 +3494,10 @@
         <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.753</v>
+        <v>0.751</v>
       </c>
       <c r="R17" t="n">
         <v>10.9</v>
@@ -3439,10 +3506,10 @@
         <v>30.2</v>
       </c>
       <c r="T17" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V17" t="n">
         <v>13.5</v>
@@ -3451,13 +3518,13 @@
         <v>7.4</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
         <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA17" t="n">
         <v>21</v>
@@ -3469,7 +3536,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>22</v>
@@ -3499,7 +3566,7 @@
         <v>18</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
@@ -3508,16 +3575,16 @@
         <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU17" t="n">
         <v>30</v>
@@ -3526,16 +3593,16 @@
         <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -3573,31 +3640,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>0.23</v>
+        <v>0.227</v>
       </c>
       <c r="H18" t="n">
         <v>48.2</v>
       </c>
       <c r="I18" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J18" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L18" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M18" t="n">
         <v>19.1</v>
@@ -3606,10 +3673,10 @@
         <v>0.374</v>
       </c>
       <c r="O18" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P18" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0.767</v>
@@ -3627,10 +3694,10 @@
         <v>20.1</v>
       </c>
       <c r="V18" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="W18" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X18" t="n">
         <v>5.2</v>
@@ -3639,16 +3706,16 @@
         <v>5.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD18" t="n">
         <v>3</v>
@@ -3663,16 +3730,16 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>2</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>9</v>
@@ -3684,7 +3751,7 @@
         <v>6</v>
       </c>
       <c r="AO18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP18" t="n">
         <v>13</v>
@@ -3702,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV18" t="n">
         <v>30</v>
@@ -3720,7 +3787,7 @@
         <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>51</v>
       </c>
       <c r="G19" t="n">
-        <v>0.301</v>
+        <v>0.311</v>
       </c>
       <c r="H19" t="n">
         <v>48.9</v>
@@ -3773,19 +3840,19 @@
         <v>35.3</v>
       </c>
       <c r="J19" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L19" t="n">
         <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
         <v>17.6</v>
@@ -3794,16 +3861,16 @@
         <v>23.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R19" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S19" t="n">
         <v>30.4</v>
       </c>
       <c r="T19" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U19" t="n">
         <v>20.8</v>
@@ -3818,7 +3885,7 @@
         <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z19" t="n">
         <v>22.2</v>
@@ -3827,13 +3894,13 @@
         <v>20</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
         <v>25</v>
@@ -3854,7 +3921,7 @@
         <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>21</v>
@@ -3863,13 +3930,13 @@
         <v>20</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>24</v>
       </c>
       <c r="AP19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ19" t="n">
         <v>18</v>
@@ -3881,13 +3948,13 @@
         <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" t="n">
         <v>32</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.573</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3964,10 +4031,10 @@
         <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O20" t="n">
         <v>17.8</v>
@@ -3979,10 +4046,10 @@
         <v>0.767</v>
       </c>
       <c r="R20" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T20" t="n">
         <v>40.4</v>
@@ -3991,22 +4058,22 @@
         <v>20.4</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
         <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z20" t="n">
         <v>20.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB20" t="n">
         <v>95.09999999999999</v>
@@ -4027,7 +4094,7 @@
         <v>10</v>
       </c>
       <c r="AH20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI20" t="n">
         <v>26</v>
@@ -4051,7 +4118,7 @@
         <v>21</v>
       </c>
       <c r="AP20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ20" t="n">
         <v>14</v>
@@ -4060,22 +4127,22 @@
         <v>23</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT20" t="n">
         <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
         <v>19</v>
@@ -4087,10 +4154,10 @@
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F21" t="n">
         <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,7 +4204,7 @@
         <v>38.3</v>
       </c>
       <c r="J21" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K21" t="n">
         <v>0.457</v>
@@ -4146,31 +4213,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O21" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P21" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R21" t="n">
         <v>10.4</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
         <v>13.8</v>
@@ -4179,7 +4246,7 @@
         <v>7.5</v>
       </c>
       <c r="X21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y21" t="n">
         <v>4.5</v>
@@ -4191,10 +4258,10 @@
         <v>20.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AD21" t="n">
         <v>3</v>
@@ -4203,13 +4270,13 @@
         <v>16</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4227,25 +4294,25 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ21" t="n">
         <v>2</v>
       </c>
       <c r="AR21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>15</v>
@@ -4254,13 +4321,13 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY21" t="n">
         <v>9</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>11</v>
       </c>
       <c r="AZ21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.671</v>
+        <v>0.676</v>
       </c>
       <c r="H22" t="n">
         <v>48.8</v>
       </c>
       <c r="I22" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J22" t="n">
         <v>80.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L22" t="n">
         <v>6</v>
@@ -4331,13 +4398,13 @@
         <v>17</v>
       </c>
       <c r="N22" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O22" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="Q22" t="n">
         <v>0.823</v>
@@ -4346,40 +4413,40 @@
         <v>10.8</v>
       </c>
       <c r="S22" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T22" t="n">
         <v>42.4</v>
       </c>
       <c r="U22" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V22" t="n">
         <v>13.9</v>
       </c>
       <c r="W22" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB22" t="n">
         <v>104.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
@@ -4391,13 +4458,13 @@
         <v>7</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
         <v>11</v>
@@ -4409,7 +4476,7 @@
         <v>19</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4424,13 +4491,13 @@
         <v>17</v>
       </c>
       <c r="AS22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="n">
         <v>14</v>
@@ -4439,13 +4506,13 @@
         <v>5</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
         <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
         <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.622</v>
+        <v>0.627</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
         <v>78.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L23" t="n">
         <v>9.4</v>
@@ -4519,31 +4586,31 @@
         <v>17.7</v>
       </c>
       <c r="P23" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S23" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U23" t="n">
         <v>20.1</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
         <v>6.5</v>
       </c>
       <c r="X23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y23" t="n">
         <v>3.9</v>
@@ -4552,13 +4619,13 @@
         <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AD23" t="n">
         <v>3</v>
@@ -4573,7 +4640,7 @@
         <v>8</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>24</v>
@@ -4594,7 +4661,7 @@
         <v>11</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
         <v>5</v>
@@ -4612,10 +4679,10 @@
         <v>6</v>
       </c>
       <c r="AU23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW23" t="n">
         <v>26</v>
@@ -4633,7 +4700,7 @@
         <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC23" t="n">
         <v>6</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E24" t="n">
         <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.527</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
@@ -4695,13 +4762,13 @@
         <v>15.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O24" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q24" t="n">
         <v>0.771</v>
@@ -4710,37 +4777,37 @@
         <v>10.4</v>
       </c>
       <c r="S24" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T24" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U24" t="n">
         <v>22.7</v>
       </c>
       <c r="V24" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W24" t="n">
         <v>7.6</v>
       </c>
       <c r="X24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y24" t="n">
         <v>4.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA24" t="n">
         <v>18.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
         <v>3</v>
@@ -4749,19 +4816,19 @@
         <v>14</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
         <v>5</v>
       </c>
       <c r="AI24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK24" t="n">
         <v>12</v>
@@ -4773,19 +4840,19 @@
         <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
         <v>25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>7</v>
@@ -4806,7 +4873,7 @@
         <v>23</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4815,7 +4882,7 @@
         <v>27</v>
       </c>
       <c r="BB24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -4847,13 +4914,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" t="n">
         <v>0.486</v>
@@ -4865,7 +4932,7 @@
         <v>39.2</v>
       </c>
       <c r="J25" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.47</v>
@@ -4877,7 +4944,7 @@
         <v>23</v>
       </c>
       <c r="N25" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O25" t="n">
         <v>18</v>
@@ -4886,7 +4953,7 @@
         <v>23.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
         <v>10</v>
@@ -4895,10 +4962,10 @@
         <v>30.3</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V25" t="n">
         <v>14.3</v>
@@ -4916,25 +4983,25 @@
         <v>20.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.2</v>
+        <v>105</v>
       </c>
       <c r="AC25" t="n">
         <v>-0.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH25" t="n">
         <v>2</v>
@@ -4967,16 +5034,16 @@
         <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV25" t="n">
         <v>18</v>
@@ -4994,7 +5061,7 @@
         <v>13</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -5029,61 +5096,61 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E26" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
         <v>32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.573</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>80.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>0.448</v>
       </c>
       <c r="L26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
         <v>18.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.341</v>
+        <v>0.345</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P26" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="R26" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="S26" t="n">
         <v>27.1</v>
       </c>
       <c r="T26" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="U26" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V26" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W26" t="n">
         <v>8.1</v>
@@ -5092,64 +5159,64 @@
         <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z26" t="n">
         <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AF26" t="n">
         <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
         <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AK26" t="n">
         <v>24</v>
       </c>
       <c r="AL26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AM26" t="n">
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
         <v>27</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
         <v>29</v>
@@ -5176,13 +5243,13 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB26" t="n">
         <v>23</v>
       </c>
       <c r="BC26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F27" t="n">
         <v>53</v>
       </c>
       <c r="G27" t="n">
-        <v>0.274</v>
+        <v>0.284</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5244,13 +5311,13 @@
         <v>0.347</v>
       </c>
       <c r="O27" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R27" t="n">
         <v>13.1</v>
@@ -5262,13 +5329,13 @@
         <v>43.8</v>
       </c>
       <c r="U27" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V27" t="n">
         <v>16.3</v>
       </c>
       <c r="W27" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X27" t="n">
         <v>4.8</v>
@@ -5280,16 +5347,16 @@
         <v>22.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC27" t="n">
         <v>-5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5307,7 +5374,7 @@
         <v>11</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
@@ -5319,16 +5386,16 @@
         <v>23</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
@@ -5337,13 +5404,13 @@
         <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU27" t="n">
         <v>24</v>
       </c>
       <c r="AV27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
@@ -5355,13 +5422,13 @@
         <v>21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -5396,67 +5463,67 @@
         <v>74</v>
       </c>
       <c r="E28" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.757</v>
+        <v>0.77</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J28" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L28" t="n">
         <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="N28" t="n">
-        <v>0.397</v>
+        <v>0.399</v>
       </c>
       <c r="O28" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="P28" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="Q28" t="n">
         <v>0.766</v>
       </c>
       <c r="R28" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T28" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U28" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V28" t="n">
         <v>13.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>4.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
         <v>18.8</v>
@@ -5465,13 +5532,13 @@
         <v>20.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>103</v>
+        <v>103.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,16 +5550,16 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
         <v>15</v>
       </c>
       <c r="AK28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
         <v>4</v>
@@ -5504,10 +5571,10 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ28" t="n">
         <v>16</v>
@@ -5522,31 +5589,31 @@
         <v>13</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>8</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY28" t="n">
         <v>15</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB28" t="n">
         <v>6</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -5575,34 +5642,34 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G29" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J29" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.467</v>
+        <v>0.465</v>
       </c>
       <c r="L29" t="n">
         <v>4.3</v>
       </c>
       <c r="M29" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="N29" t="n">
         <v>0.316</v>
@@ -5626,7 +5693,7 @@
         <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V29" t="n">
         <v>14.7</v>
@@ -5638,13 +5705,13 @@
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB29" t="n">
         <v>99.3</v>
@@ -5653,28 +5720,28 @@
         <v>-6.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH29" t="n">
         <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>29</v>
@@ -5686,16 +5753,16 @@
         <v>30</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="n">
         <v>20</v>
       </c>
       <c r="AQ29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
         <v>28</v>
@@ -5707,19 +5774,19 @@
         <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>26</v>
       </c>
       <c r="AY29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -5757,61 +5824,61 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E30" t="n">
         <v>36</v>
       </c>
       <c r="F30" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>0.493</v>
+        <v>0.48</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J30" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M30" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O30" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P30" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R30" t="n">
         <v>10.9</v>
       </c>
       <c r="S30" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="T30" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="U30" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V30" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W30" t="n">
         <v>7.7</v>
@@ -5820,40 +5887,40 @@
         <v>5.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="AA30" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="AD30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI30" t="n">
         <v>13</v>
       </c>
-      <c r="AE30" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>12</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="n">
         <v>10</v>
@@ -5862,10 +5929,10 @@
         <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5877,7 +5944,7 @@
         <v>9</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
         <v>27</v>
@@ -5886,7 +5953,7 @@
         <v>27</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV30" t="n">
         <v>17</v>
@@ -5895,7 +5962,7 @@
         <v>7</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>20</v>
@@ -5907,7 +5974,7 @@
         <v>2</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
@@ -5939,55 +6006,55 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
         <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G31" t="n">
-        <v>0.247</v>
+        <v>0.243</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J31" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O31" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P31" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R31" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S31" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U31" t="n">
         <v>19.7</v>
@@ -6011,13 +6078,13 @@
         <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.9</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6032,13 +6099,13 @@
         <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ31" t="n">
         <v>5</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>27</v>
@@ -6050,22 +6117,22 @@
         <v>27</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ31" t="n">
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS31" t="n">
         <v>25</v>
       </c>
       <c r="AT31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>28</v>
@@ -6089,7 +6156,7 @@
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-31-2010-11</t>
+          <t>2011-03-31</t>
         </is>
       </c>
     </row>
